--- a/自动化用例覆盖清单.xlsx
+++ b/自动化用例覆盖清单.xlsx
@@ -1701,7 +1701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2405,292 +2405,292 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>M4-04</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>插件说明指引与「设置 → 内置插件」联动入口</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>读 intro/「官方」徽标→点「插件说明」</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>指引描述出现且含「设置 → 内置插件」</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>M4-05</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>插件详情页：组件清单与运行状态</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>「查看 X」进详情→返回</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>返回插件列表/共 N 个/组件状态词/「启用组件 X」存在（不点击）；返回后清单一致</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>M4-06</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>安装表单引导与安装源（不实际安装）</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>M4-01</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>打开添加插件→展开/收起引导</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>输入框 aria 包名或地址+安装（空输入禁用）+安装源；引导含示例/填入示例/安全提示；收起复原</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>M4-07</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>设置 → 内置插件只读清单</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>设置→内置插件</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>intro/搜索框/分组计数&gt;0；无组件启停控件（只读）</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>M5-01</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>上传知识文件（附件登记）</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>新会话</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>「添加文件或调用指令」上传 kb-sample.md</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>待发送附件区登记</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>⏭ 桌面附件链路自动化边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>M5-02</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>提问命中知识文件内容</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>M5-01</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>问文件中的机密代号</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>回复含一次性随机标记</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>⏭ 同 M5-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>M6-01</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>复制回复到剪贴板</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>存在回复</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>点复制→读剪贴板</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>剪贴板内容与回复正文一致</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>M6-02</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>点赞出现感谢反馈</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>存在回复</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>点「好的回答」</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>toast 含「感谢」</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>M6-03</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>点踩提交反馈表单</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>存在回复</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>点「有问题的回答」→选其他→提交</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>dialog 出现且提交后关闭</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>M6-04</t>
+          <t>M5-02</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>在新对话中分支</t>
+          <t>提问命中知识文件内容</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>存在回复</t>
+          <t>M5-01</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>点「在新对话中分支」</t>
+          <t>问文件中的机密代号</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>跳转新会话，输入区可用</t>
+          <t>回复含一次性随机标记</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2708,26 +2708,26 @@
           <t>✅ 通过</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>⏭ 同 M5-01</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>M7-01</t>
+          <t>M6-01</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>回合展示用量，tok 可解析且 &gt;0</t>
+          <t>复制回复到剪贴板</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>读「用量」按钮文本并解析</t>
+          <t>点复制→读剪贴板</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>解析值 &gt;0</t>
+          <t>剪贴板内容与回复正文一致</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2769,17 +2769,17 @@
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>M7-02</t>
+          <t>M6-02</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>回合展示用时，秒数 ≥0</t>
+          <t>点赞出现感谢反馈</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>读「用时」按钮文本并解析</t>
+          <t>点「好的回答」</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>秒数 ≥0</t>
+          <t>toast 含「感谢」</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2821,17 +2821,17 @@
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>M7-03</t>
+          <t>M6-03</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>用量明细弹层展示精确 token 数</t>
+          <t>点踩提交反馈表单</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>点「用量」</t>
+          <t>点「有问题的回答」→选其他→提交</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>弹层含千分位精确值（如 9,792 tok）</t>
+          <t>dialog 出现且提交后关闭</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -2873,17 +2873,17 @@
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>M7-04</t>
+          <t>M6-04</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>用时明细弹层可打开</t>
+          <t>在新对话中分支</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>点「用时」</t>
+          <t>点「在新对话中分支」</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>弹层含该回合原文片段</t>
+          <t>跳转新会话，输入区可用</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2925,7 +2925,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>M7-05</t>
+          <t>M7-01</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>会话统计条展示轮次与缓存命中</t>
+          <t>回合展示用量，tok 可解析且 &gt;0</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>多轮会话</t>
+          <t>存在回复</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>读会话统计条</t>
+          <t>读「用量」按钮文本并解析</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>匹配 /轮.*步/ 且含 tok/s</t>
+          <t>解析值 &gt;0</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2974,35 +2974,35 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>M8-01</t>
+          <t>M7-02</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>输入区与控件</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>指令面板打开与关闭</t>
+          <t>回合展示用时，秒数 ≥0</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>存在回复</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>点「添加文件或调用指令」</t>
+          <t>读「用时」按钮文本并解析</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>列出指令（文件/目标/计划/反馈/压缩/权限/模型/下载日志）；Esc 关闭</t>
+          <t>秒数 ≥0</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -3029,32 +3029,32 @@
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>M8-02</t>
+          <t>M7-03</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>输入区与控件</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>模型选择器展示当前模型与可选列表</t>
+          <t>用量明细弹层展示精确 token 数</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>存在回复</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>读当前模型→打开模型菜单</t>
+          <t>点「用量」</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>菜单包含当前模型</t>
+          <t>弹层含千分位精确值（如 9,792 tok）</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -3078,35 +3078,35 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="38" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>M8-03</t>
+          <t>M7-04</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>输入区与控件</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>访问模式（权限选择）菜单</t>
+          <t>用时明细弹层可打开</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>存在回复</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>读当前模式→打开菜单</t>
+          <t>点「用时」</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>选项含 仅可查看/工作区内修改/完全权限，含当前模式</t>
+          <t>弹层含该回合原文片段</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -3133,32 +3133,32 @@
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>M8-04</t>
+          <t>M7-05</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>会话搜索过滤（查询）</t>
+          <t>会话统计条展示轮次与缓存命中</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>自造关键字会话</t>
+          <t>多轮会话</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>搜索关键字→搜索不存在串</t>
+          <t>读会话统计条</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>关键字命中 &gt;0；不存在串命中 0</t>
+          <t>匹配 /轮.*步/ 且含 tok/s</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>造数</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -3182,20 +3182,20 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="38" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>M8-05</t>
+          <t>M8-01</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>设置中心</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>设置导航项切换</t>
+          <t>指令面板打开与关闭</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>逐个切 通用设置/模型/内置插件/Agent 预设</t>
+          <t>点「添加文件或调用指令」</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>均可切换，弹窗保持</t>
+          <t>列出指令（文件/目标/计划/反馈/压缩/权限/模型/下载日志）；Esc 关闭</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -3237,17 +3237,17 @@
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M8-06</t>
+          <t>M8-02</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>设置中心</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>主题切换背景亮度变化</t>
+          <t>模型选择器展示当前模型与可选列表</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>深色↔浅色</t>
+          <t>读当前模型→打开模型菜单</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>深色亮度 &lt;80，浅色 &gt;150</t>
+          <t>菜单包含当前模型</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3286,35 +3286,35 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="38" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>M8-07</t>
+          <t>M8-03</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>右侧工作面板</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>右侧栏页签切换</t>
+          <t>访问模式（权限选择）菜单</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>会话中已发消息</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>展开右栏→切对话/轨迹</t>
+          <t>读当前模式→打开菜单</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>常驻页签可见可切</t>
+          <t>选项含 仅可查看/工作区内修改/完全权限，含当前模式</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -3341,32 +3341,32 @@
     <row r="35" ht="22" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M8-08</t>
+          <t>M8-04</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>右侧工作面板</t>
+          <t>会话治理</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>右侧栏布局按钮可见</t>
+          <t>会话搜索过滤（查询）</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>会话中已发消息</t>
+          <t>自造关键字会话</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>展开右栏</t>
+          <t>搜索关键字→搜索不存在串</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>新标签页/分栏/全屏可见</t>
+          <t>关键字命中 &gt;0；不存在串命中 0</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>造数</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -3393,32 +3393,32 @@
     <row r="36" ht="22" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>M8-09</t>
+          <t>M8-05</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>设置中心</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>切换会话（树行点击→转录本切换）</t>
+          <t>设置导航项切换</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>会话 A 带标记消息</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>新建会话 B→树里点回 A</t>
+          <t>逐个切 通用设置/模型/内置插件/Agent 预设</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>转录本显示 A 的消息，行 aria-selected</t>
+          <t>均可切换，弹窗保持</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>✅ 通过（重试一次）</t>
+          <t>✅ 通过</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -3442,20 +3442,20 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M8-06</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>设置中心</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>左上角折叠/打开会话页</t>
+          <t>主题切换背景亮度变化</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>点「收起侧边栏」→点「打开侧边栏」</t>
+          <t>深色↔浅色</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>折叠成图标栏（展开态内容隐藏）；展开后控件回归</t>
+          <t>深色亮度 &lt;80，浅色 &gt;150</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -3497,240 +3497,240 @@
     <row r="38" ht="22" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
+          <t>M8-07</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>右侧栏页签切换</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>会话中已发消息</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>展开右栏→切对话/轨迹</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>常驻页签可见可切</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>M8-08</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>右侧栏布局按钮可见</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>会话中已发消息</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>展开右栏</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>新标签页/分栏/全屏可见</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>M8-09</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>切换会话（树行点击→转录本切换）</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>会话 A 带标记消息</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>新建会话 B→树里点回 A</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>转录本显示 A 的消息，行 aria-selected</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过（重试一次）</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>M8-10</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>左上角折叠/打开会话页</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>点「收起侧边栏」→点「打开侧边栏」</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>折叠成图标栏（展开态内容隐藏）；展开后控件回归</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>M8-11</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>会话治理</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>视图选项分组（按工作区↔按工作区树）</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>已登录</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>开视图选项菜单→切换分组方式</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>菜单含分组/排序项；切换后树仍可用</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="38" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>M8-12</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>设置中心</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>设置应用控件：字号增大/减小即时生效</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>已登录</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>设置→增大字号→减小字号</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>字号值实际变化（eline 设置无独立「应用」按钮，改动即时生效）</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="38" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>M8-13</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>输入区与控件</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>模型思考程度（推理等级）展示</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>会话中</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>读 trigger aria /按钮第二行；开菜单探测切换行</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>展示当前等级（如 High）；切换行随模型目录下发（本部署未下发，记录差异）</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>M8-14</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>右侧工作面板</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>右栏功能：打开工作区文件/新建终端/打开浏览器</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>新会话</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>「开始」落地页依次点 新建终端/工作区文件/浏览器</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>终端页签（shell 名）+xterm；文件面板（重新读取等）；浏览器仅桌面端有入口（web 无 webview，记录差异）</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>M8-15</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>右侧工作面板</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>右栏布局：分栏/最大化（全屏）/收起</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>新会话</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>分栏→全屏→收起 依次实点</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>分栏后控件成对；全屏后变「退出全屏」；收起后「打开右侧边栏」回归</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3757,500 +3757,500 @@
     <row r="43" ht="38" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>M8-12</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>设置中心</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>设置应用控件：字号增大/减小即时生效</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>设置→增大字号→减小字号</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>字号值实际变化（eline 设置无独立「应用」按钮，改动即时生效）</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>M8-13</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>输入区与控件</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>模型思考程度（推理等级）展示</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>会话中</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>读 trigger aria /按钮第二行；开菜单探测切换行</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>展示当前等级（如 High）；切换行随模型目录下发（本部署未下发，记录差异）</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>M8-14</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>右栏功能：打开工作区文件/新建终端/打开浏览器</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>新会话</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>「开始」落地页依次点 新建终端/工作区文件/浏览器</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>终端页签（shell 名）+xterm；文件面板（重新读取等）；浏览器仅桌面端有入口（web 无 webview，记录差异）</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>M8-15</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>右栏布局：分栏/最大化（全屏）/收起</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>新会话</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>分栏→全屏→收起 依次实点</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>分栏后控件成对；全屏后变「退出全屏」；收起后「打开右侧边栏」回归</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
           <t>M9-01</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>添加工作区（创建新工作区）</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>RPC workspace/create（UI 入口拉起 OS 目录选择器）</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>工作区树出现新行</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>M9-02</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>在指定工作区中新建会话</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>M9-01</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>hover 工作区行→「在 X 中新建会话」</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>会话归属该工作区</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>M9-03</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>新工作区内发消息</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>M9-02</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>发消息</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>用户消息上屏</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>M9-04</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>重命名工作区</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>M9-01</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>行操作菜单→重命名→填新标题</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>树行标题更新</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>M9-05</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>删除工作区</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>M9-04</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>行操作菜单→删除→确认</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>树行消失；应用仍可用</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="38" customHeight="1">
-      <c r="B48" s="4" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="38" customHeight="1">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>M9-06</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>输入区与控件</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Agent 预设（模式选择）往返</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>首页 hero</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>五模式切换往返</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>外贸专家/标准/PTC/极简/创造 可选；chip 文本更新并可复原</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J48" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="38" customHeight="1">
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>M9-07</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>输入区与控件</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>模型选择（当前模型与可选目录）</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>首页/会话</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>读当前模型→开菜单→下钻模型目录</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>菜单含当前模型；目录清单记录（DeepSeek-V4-Pro / V41-Flash）</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="38" customHeight="1">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>M9-08</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>选择工作区按钮（当前工作区/菜单/添加入口）</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>首页 hero</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>读按钮文本→开菜单→重选当前项</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>按钮显示当前工作区；菜单含列表+「添加工作区…」；幂等</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>M10-01</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>会话治理</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>@ 引用会话/文件</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>会话输入区</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>输入「@」</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>弹出历史会话引用列表（标题+相对时间），Esc 关闭</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>M10-02</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>会话治理</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>重命名会话</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>会话行操作菜单</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>菜单→重命名→填唯一标题→回车</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>树行标题更新（仅对已落库会话生效）</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4277,32 +4277,32 @@
     <row r="53" ht="38" customHeight="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>M10-03</t>
+          <t>M9-07</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>归档会话与归档过滤</t>
+          <t>模型选择（当前模型与可选目录）</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>会话行操作菜单 + 视图选项</t>
+          <t>首页/会话</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>归档→仅显示已归档→取消归档→隐藏已归档</t>
+          <t>读当前模型→开菜单→下钻模型目录</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>归档后默认视图移除；归档视图可见；取消后恢复</t>
+          <t>菜单含当前模型；目录清单记录（DeepSeek-V4-Pro / V41-Flash）</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -4326,35 +4326,35 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1">
+    <row r="54" ht="38" customHeight="1">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>M10-04</t>
+          <t>M9-08</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>分叉会话</t>
+          <t>选择工作区按钮（当前工作区/菜单/添加入口）</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>会话行操作菜单</t>
+          <t>首页 hero</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>搜索定位→菜单→分叉会话</t>
+          <t>读按钮文本→开菜单→重选当前项</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>生成「原标题 (N)」副本（搜索计数 +1）</t>
+          <t>按钮显示当前工作区；菜单含列表+「添加工作区…」；幂等</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4381,32 +4381,32 @@
     <row r="55" ht="38" customHeight="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>M10-05</t>
+          <t>M10-01</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>设置中心</t>
+          <t>会话治理</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>快捷键编辑器</t>
+          <t>@ 引用会话/文件</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>设置→编辑快捷键</t>
+          <t>会话输入区</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>搜索「会话」读绑定</t>
+          <t>输入「@」</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>清单含新建/重命名/分叉/归档等；读到归档绑定</t>
+          <t>弹出历史会话引用列表（标题+相对时间），Esc 关闭</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -4433,188 +4433,188 @@
     <row r="56" ht="22" customHeight="1">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>M10-06</t>
+          <t>M10-02</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>重命名会话</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>会话行操作菜单</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>菜单→重命名→填唯一标题→回车</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>树行标题更新（仅对已落库会话生效）</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="38" customHeight="1">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>M10-03</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>归档会话与归档过滤</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>会话行操作菜单 + 视图选项</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>归档→仅显示已归档→取消归档→隐藏已归档</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>归档后默认视图移除；归档视图可见；取消后恢复</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>M10-04</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>分叉会话</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>会话行操作菜单</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>搜索定位→菜单→分叉会话</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>生成「原标题 (N)」副本（搜索计数 +1）</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="38" customHeight="1">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>M10-05</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
           <t>设置中心</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>语言切换（中/英）</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>设置→语言</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>切 English→切回中文（finally 保证恢复）</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>英文文案生效；恢复后 UI 复原</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>M10-07</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>设置中心</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>模型提供商编辑器</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>设置→模型→编辑 中转站</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>打开弹层→断言输入行→取消</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>弹层含模型配置输入行/添加模型；取消不落盘</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="38" customHeight="1">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>M10-08</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>设置中心</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>设置功能开关与选择器</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>设置→通用设置</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>翻转 2 个 switch 并复原；开「排队发送」菜单</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>开关状态翻转并复原；排队发送为下拉选择器</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>M10-09</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>导出与外部集成</t>
-        </is>
-      </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Session 导出下载</t>
+          <t>快捷键编辑器</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>会话「更多操作」</t>
+          <t>设置→编辑快捷键</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>点「下载 Session 日志」</t>
+          <t>搜索「会话」读绑定</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>触发 download 事件，文件名为 .zip</t>
+          <t>清单含新建/重命名/分叉/归档等；读到归档绑定</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -4641,32 +4641,32 @@
     <row r="60" ht="22" customHeight="1">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>M10-10</t>
+          <t>M10-06</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>导出与外部集成</t>
+          <t>设置中心</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>「更多打开方式」菜单</t>
+          <t>语言切换（中/英）</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>会话头部</t>
+          <t>设置→语言</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>打开菜单断言（不点击 VS Code）</t>
+          <t>切 English→切回中文（finally 保证恢复）</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>含 文件资源管理器（默认）/VS Code</t>
+          <t>英文文案生效；恢复后 UI 复原</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4693,32 +4693,32 @@
     <row r="61" ht="22" customHeight="1">
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>M10-11</t>
+          <t>M10-07</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>用量/用时</t>
+          <t>设置中心</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>状态栏统计条交互</t>
+          <t>模型提供商编辑器</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>会话底部统计条</t>
+          <t>设置→模型→编辑 中转站</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>逐个点 轮步/tok/上下文按钮</t>
+          <t>打开弹层→断言输入行→取消</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>三按钮可见可点，无错误</t>
+          <t>弹层含模型配置输入行/添加模型；取消不落盘</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
@@ -4742,35 +4742,35 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1">
+    <row r="62" ht="38" customHeight="1">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>M10-12</t>
+          <t>M10-08</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>右侧工作面板</t>
+          <t>设置中心</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>终端↔工作区文件联动</t>
+          <t>设置功能开关与选择器</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>右栏终端 + 文件面板</t>
+          <t>设置→通用设置</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>终端 echo 建文件→文件面板断言→清理</t>
+          <t>翻转 2 个 switch 并复原；开「排队发送」菜单</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>面板即时可见新文件</t>
+          <t>开关状态翻转并复原；排队发送为下拉选择器</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4797,37 +4797,37 @@
     <row r="63" ht="22" customHeight="1">
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>M10-13</t>
+          <t>M10-09</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>右侧工作面板</t>
+          <t>导出与外部集成</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>浏览器页签导航（占位）</t>
+          <t>Session 导出下载</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>桌面端右栏浏览器页签</t>
+          <t>会话「更多操作」</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>地址栏输入地址断言导航</t>
+          <t>点「下载 Session 日志」</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>占位待补：web 无入口，入口断言见 M8-14</t>
+          <t>触发 download 事件，文件名为 .zip</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>electron</t>
+          <t>双端</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -4835,79 +4835,287 @@
           <t>否</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>—（占位）</t>
-        </is>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>—（占位）</t>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="B64" s="4" t="inlineStr">
         <is>
+          <t>M10-10</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>导出与外部集成</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>「更多打开方式」菜单</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>会话头部</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>打开菜单断言（不点击 VS Code）</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>含 文件资源管理器（默认）/VS Code</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>M10-11</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>用量/用时</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>状态栏统计条交互</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>会话底部统计条</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>逐个点 轮步/tok/上下文按钮</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>三按钮可见可点，无错误</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>M10-12</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>终端↔工作区文件联动</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>右栏终端 + 文件面板</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>终端 echo 建文件→文件面板断言→清理</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>面板即时可见新文件</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>M10-13</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>浏览器页签导航（占位）</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>桌面端右栏浏览器页签</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>地址栏输入地址断言导航</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>占位待补：web 无入口，入口断言见 M8-14</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>electron</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>—（占位）</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>—（占位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
           <t>M10-14</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>设置中心</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Agent 预设辅助弹层</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>设置→Agent 预设</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>点「模式说明/如何使用: 标准模式」</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>弹层有内容，可关闭</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="K64" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1"/>
-    <row r="66" ht="22" customHeight="1">
-      <c r="B66" s="5" t="inlineStr">
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>结果口径：2026-10-16/17 两轮全量运行（模型渠道修复后）。「✅ 通过（重试一次）」= 首试因会话标题入库延迟未命中、重试通过（已加显式等待加固）。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="B67" s="5" t="inlineStr">
+    <row r="71" ht="22" customHeight="1">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>「⏭ 桌面附件链路自动化边界」：桌面端附件选择走非 Electron dialog 的原生链路，Playwright 无法驱动（spec 内有完整说明）；web 端已实测覆盖。</t>
         </is>
@@ -5474,7 +5682,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
+    <row r="25" ht="38" customHeight="1">
       <c r="B25" s="3" t="n">
         <v>21</v>
       </c>
@@ -5490,12 +5698,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>M4 已到表单；真实安装刻意不做</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>维持现状（人工验证）</t>
+          <t>插件详情已补用例 M4-05；真实安装刻意不做（不污染被测环境）</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>真实安装维持人工验证</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5627,7 +5835,7 @@
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="38" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>反例ID</t>
@@ -5912,32 +6120,32 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>M5-01A</t>
+          <t>M4-05A</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>M5-01</t>
+          <t>M4-05</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>附件问答</t>
+          <t>插件管理</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>发送前撤回：点「移除文件 X」→ 附件区清空（另记录：附件草稿跨会话保持）</t>
+          <t>插件详情 ↔ 列表往返 2 轮 → 清单不丢行不换序</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>幂等</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>双端</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -5945,41 +6153,41 @@
           <t>已实现</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>—（自动化边界）</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>M6-01A</t>
+          <t>M4-06A</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>M6-01/04</t>
+          <t>M4-06</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>消息操作</t>
+          <t>插件管理</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>空会话无回合操作条（复制/分支按钮均不存在）</t>
+          <t>安装表单非法包名 → 校验拒绝/禁用态，无安装副作用</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>形态缺失</t>
+          <t>无效输入</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -5992,9 +6200,9 @@
           <t>已实现</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -6006,27 +6214,27 @@
     <row r="12" ht="38" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>M6-02A</t>
+          <t>M4-07A</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>M6-02</t>
+          <t>M4-07</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>消息操作</t>
+          <t>插件管理</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>点赞弹出的反馈表单取消 → 无副作用、表单关闭</t>
+          <t>内置插件搜索不存在串 → 「没有匹配」空态；清空后恢复</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>容错</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -6039,9 +6247,9 @@
           <t>已实现</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>—（web 弹窗缺陷待修）</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -6053,69 +6261,69 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>M6-03A</t>
+          <t>M5-01A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>M6-03</t>
+          <t>M5-01</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>附件问答</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>发送前撤回：点「移除文件 X」→ 附件区清空（另记录：附件草稿跨会话保持）</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>—（自动化边界）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>M6-01A</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>M6-01/04</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>消息操作</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>点踩表单取消 → 不提交、dialog 关闭、转录本无变化</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>M7-01A</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>M7-01/02</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>用量/用时</t>
-        </is>
-      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>空会话无用量按钮/用时节点</t>
+          <t>空会话无回合操作条（复制/分支按钮均不存在）</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -6147,27 +6355,27 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>M7-03A</t>
+          <t>M6-02A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>M7-03/04</t>
+          <t>M6-02</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>用量/用时</t>
+          <t>消息操作</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>用量/用时明细弹层 关闭→重开 内容一致（往返幂等）</t>
+          <t>点赞弹出的反馈表单取消 → 无副作用、表单关闭</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>幂等</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -6194,27 +6402,27 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>M10-11A</t>
+          <t>M6-03A</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>M10-11</t>
+          <t>M6-03</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>用量/用时</t>
+          <t>消息操作</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>统计条按钮快速连点两轮 → 按钮完整保留、无异常</t>
+          <t>点踩表单取消 → 不提交、dialog 关闭、转录本无变化</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>容错</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -6241,86 +6449,86 @@
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>M8-01A</t>
+          <t>M7-01A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>M8-01</t>
+          <t>M7-01/02</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>输入区与控件</t>
+          <t>用量/用时</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>指令面板 Esc 关闭→重开，指令清单一致</t>
+          <t>空会话无用量按钮/用时节点</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>形态缺失</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>M7-03A</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>M7-03/04</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>用量/用时</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>用量/用时明细弹层 关闭→重开 内容一致（往返幂等）</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>幂等</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>M8-02A</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>M8-02</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>输入区与控件</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>模型菜单 Esc 取消 → 当前模型不变</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
           <t>✅ 通过</t>
@@ -6332,30 +6540,30 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="38" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>M8-03A</t>
+          <t>M10-11A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>M8-03</t>
+          <t>M10-11</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>输入区与控件</t>
+          <t>用量/用时</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>权限菜单 Esc 取消 → 当前权限不变</t>
+          <t>统计条按钮快速连点两轮 → 按钮完整保留、无异常</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>容错</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -6382,12 +6590,12 @@
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>M9-06A</t>
+          <t>M8-01A</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>M9-06</t>
+          <t>M8-01</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -6397,12 +6605,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>模式菜单 Esc 取消 → chip 不变</t>
+          <t>指令面板 Esc 关闭→重开，指令清单一致</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>幂等</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -6429,12 +6637,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>M9-07A</t>
+          <t>M8-02A</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>M9-07</t>
+          <t>M8-02</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -6444,7 +6652,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>模型目录下钻后返回 → 当前模型不变</t>
+          <t>模型菜单 Esc 取消 → 当前模型不变</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6473,30 +6681,30 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="38" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>M8-04A</t>
+          <t>M8-03A</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>M8-04</t>
+          <t>M8-03</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>正则元字符/特殊字符搜索 → 返回计数不崩溃、搜索框可用</t>
+          <t>权限菜单 Esc 取消 → 当前权限不变</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>容错</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -6523,27 +6731,27 @@
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>M8-10A</t>
+          <t>M9-06A</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>M8-10</t>
+          <t>M9-06</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>会话治理</t>
+          <t>输入区与控件</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>折叠↔展开循环 2 轮 → 状态一致</t>
+          <t>模式菜单 Esc 取消 → chip 不变</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>幂等</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -6570,74 +6778,74 @@
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>M8-11A</t>
+          <t>M9-07A</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>M8-11</t>
+          <t>M9-07</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>输入区与控件</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>模型目录下钻后返回 → 当前模型不变</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>M8-04A</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>M8-04</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>会话治理</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>视图菜单 Esc 取消 → 工作区树仍可用</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>M10-01A</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>M10-01</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>会话治理</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>@ 引用列表 Esc → 完全关闭无残留</t>
+          <t>正则元字符/特殊字符搜索 → 返回计数不崩溃、搜索框可用</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>容错</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -6664,12 +6872,12 @@
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>M10-02A</t>
+          <t>M8-10A</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>M10-02</t>
+          <t>M8-10</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -6679,12 +6887,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>重命名会话清空名称确认 → 被拒，标题不变</t>
+          <t>折叠↔展开循环 2 轮 → 状态一致</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>无效输入</t>
+          <t>幂等</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -6711,262 +6919,262 @@
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>M8-11A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>M8-11</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>视图菜单 Esc 取消 → 工作区树仍可用</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>M10-01A</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>M10-01</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>@ 引用列表 Esc → 完全关闭无残留</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>M10-02A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>M10-02</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>会话治理</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>重命名会话清空名称确认 → 被拒，标题不变</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>无效输入</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>M10-04A</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>M10-04</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>会话治理</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>空会话不落库 → 治理菜单不可达</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>形态缺失</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>M9-01A</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>M9-01</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>工作区</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>RPC 未知方法 / 空 path 创建 → 结构化错误被拒，不静默成功</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>无效输入</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="38" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>M9-04A</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>M9-04</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>工作区</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>工作区空名称重命名 → 被拒标题不变（临时工作区，自清理）</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>无效输入</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="38" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>M9-05A</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>M9-05</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>工作区</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>删除工作区确认框取消 → 工作区保留（临时工作区，自清理）</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>M9-08A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>M9-08</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>工作区</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>选择工作区菜单 Esc → 当前工作区不变</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>M8-05A</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>M8-05</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>设置中心</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>设置弹窗 Esc 关闭 → 重开导航项正常</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>幂等</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -6993,27 +7201,27 @@
     <row r="33" ht="38" customHeight="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M8-06A</t>
+          <t>M9-05A</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>M8-06</t>
+          <t>M9-05</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>设置中心</t>
+          <t>工作区</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>主题切走再复原 → 亮度回到初始值（±25 容差）</t>
+          <t>删除工作区确认框取消 → 工作区保留（临时工作区，自清理）</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>幂等</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -7037,30 +7245,30 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="38" customHeight="1">
+    <row r="34" ht="22" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>M8-12A</t>
+          <t>M9-08A</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>M8-12</t>
+          <t>M9-08</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>设置中心</t>
+          <t>工作区</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>字号连增 12 次/连减 30 次 → 有上下界（≤48/≥8px）并复原</t>
+          <t>选择工作区菜单 Esc → 当前工作区不变</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>边界 clamp</t>
+          <t>取消无害</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -7087,12 +7295,12 @@
     <row r="35" ht="22" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M10-05A</t>
+          <t>M8-05A</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>M10-05</t>
+          <t>M8-05</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -7102,12 +7310,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>快捷键搜索不存在功能 → 无任何绑定行</t>
+          <t>设置弹窗 Esc 关闭 → 重开导航项正常</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>无效输入</t>
+          <t>幂等</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -7131,15 +7339,15 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
+    <row r="36" ht="38" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>M10-06A</t>
+          <t>M8-06A</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>M10-06</t>
+          <t>M8-06</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -7149,12 +7357,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>语言菜单 Esc 取消 → 保持中文（锚点仍在）</t>
+          <t>主题切走再复原 → 亮度回到初始值（±25 容差）</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>幂等</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -7181,12 +7389,12 @@
     <row r="37" ht="38" customHeight="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M10-07A</t>
+          <t>M8-12A</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>M10-07</t>
+          <t>M8-12</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -7196,12 +7404,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>提供商编辑器改字段后取消 → 重开字段为原值（不落盘）</t>
+          <t>字号连增 12 次/连减 30 次 → 有上下界（≤48/≥8px）并复原</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>边界 clamp</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -7225,15 +7433,15 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="38" customHeight="1">
+    <row r="38" ht="22" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>M10-08A</t>
+          <t>M10-05A</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>M10-08</t>
+          <t>M10-05</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -7243,12 +7451,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>排队发送选择器 Esc 取消 → 两个功能开关状态不变</t>
+          <t>快捷键搜索不存在功能 → 无任何绑定行</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>取消无害</t>
+          <t>无效输入</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -7275,168 +7483,168 @@
     <row r="39" ht="22" customHeight="1">
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>M10-06A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>M10-06</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>设置中心</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>语言菜单 Esc 取消 → 保持中文（锚点仍在）</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>M10-07A</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>M10-07</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>设置中心</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>提供商编辑器改字段后取消 → 重开字段为原值（不落盘）</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>M10-08A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>M10-08</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>设置中心</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>排队发送选择器 Esc 取消 → 两个功能开关状态不变</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>取消无害</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>M10-14A</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>M10-14</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>设置中心</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>预设辅助弹层 Esc → 设置弹窗仍在、无异常</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>取消无害</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>M8-07A</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>M8-07</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>右侧工作面板</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>对话↔轨迹往返切换 2 轮 → 回到对话页签</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>幂等</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>M8-08A</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>M8-08</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>右侧工作面板</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>右栏收起↔展开循环 2 轮 → 控件状态一致</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>幂等</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="38" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>M8-14A</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>M8-14</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>右侧工作面板</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>浏览器入口按形态存在性负断言：web 无 / electron 有</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>形态缺失</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -7463,201 +7671,342 @@
     <row r="43" ht="22" customHeight="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>M8-07A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>M8-07</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>对话↔轨迹往返切换 2 轮 → 回到对话页签</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>幂等</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>M8-08A</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>M8-08</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>右栏收起↔展开循环 2 轮 → 控件状态一致</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>幂等</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>M8-14A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>M8-14</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>右侧工作面板</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>浏览器入口按形态存在性负断言：web 无 / electron 有</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>形态缺失</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>M8-15A</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>M8-15</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>右侧工作面板</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>全屏↔退出全屏循环 2 轮 → 可正常收起/展开</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>幂等</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="38" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>M10-12A</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>M10-12</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>右侧工作面板</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>终端执行非法命令 → 报错后仍可执行新命令（web 断言文本，桌面宽松）</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>容错</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>M10-09A</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>M10-09</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>导出与外部集成</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>空会话无「更多操作」导出入口</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>形态缺失</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="38" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>M10-10A</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>M10-10</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>导出与外部集成</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>打开方式菜单 Esc 关闭 → 可重开且菜单项齐全</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>幂等</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>双端</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>双端</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>已实现</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>✅ 通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>✅ 通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>反例原则：操作无痕恢复（开关/主题/字号/临时工作区用例内复原）；不做无法判定的 LLM 负向断言。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="5" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>五类反例：无效输入被拒 / 取消路径无害 / 幂等往返 / 边界 clamp / 容错韧性。web 专属与桌面附件边界项同正例口径。</t>
         </is>
@@ -7677,7 +8026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7778,117 +8127,129 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>M5-02</t>
+          <t>M4-04</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>同 M3-02：LLM 负向不可判定</t>
+          <t>说明面板为只读指引文本，无有效负路径（展开/收起同型于 M4-06 引导开关）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>M7-02</t>
+          <t>M5-02</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>并入 M7-01A（空会话无用时节点）</t>
+          <t>同 M3-02：LLM 负向不可判定</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>M7-04</t>
+          <t>M7-02</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>并入 M7-03A（用时明细往返）</t>
+          <t>并入 M7-01A（空会话无用时节点）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>M7-04</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>并入 M7-03A（用时明细往返）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>M7-05</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>统计条格式反例价值低；连点容错见 M10-11A</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="38" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>M8-13</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>本部署未下发推理等级切换行，负路径无可执行对象（正例已记录差异）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>M8-09</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>「切换到不存在的会话」无操作对象，不可构造</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="38" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="38" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>M10-03</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>归档活跃会话后的「选择一个工作区开始」空态与自愈已内含于 M10-03 正例</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>M9-02 / M9-03</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>空消息被拒与 M3-01A 重合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>M9-02 / M9-03</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>空消息被拒与 M3-01A 重合</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>M10-13</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>占位用例（浏览器导航），无反例</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="5" t="inlineStr">
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>这些测试项不单独实现反例：或其正例本身已含负断言，或负路径不可构造/不可判定，或与已实现反例重合。</t>
         </is>
@@ -8031,7 +8392,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>插件管理</t>
@@ -8052,7 +8413,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>侧栏插件页、清单、添加表单、启停 aria-checked</t>
+          <t>侧栏插件页、清单、添加表单、启停、说明指引、详情组件清单、安装引导与安装源、内置插件只读清单</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8656,7 @@
       <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60 条用例 × web/electron 双形态</t>
+          <t>64 条用例 × web/electron 双形态</t>
         </is>
       </c>
     </row>
